--- a/data/Mission.xlsx
+++ b/data/Mission.xlsx
@@ -463,117 +463,9 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bit_index</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>gfk:Condition</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>fk:Reward</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
